--- a/ExcelToJSONConverter/excel/region.xlsx
+++ b/ExcelToJSONConverter/excel/region.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585637FC-515E-46C5-BDEE-5DB3732B09AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{306C6822-B4EC-4D30-94C9-0D1997BD6DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21990" yWindow="2940" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2550" yWindow="3240" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>

--- a/ExcelToJSONConverter/excel/region.xlsx
+++ b/ExcelToJSONConverter/excel/region.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{306C6822-B4EC-4D30-94C9-0D1997BD6DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043F41A1-8746-4A8F-B7CE-7B6237AA10F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="3240" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="285" yWindow="2775" windowWidth="16200" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -29,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -135,7 +133,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>LiuBei, GuanYu, ZhangFei</t>
+    <t>CaoRen,XiahouDun,ZhangLiao,XiahouYuan,XunYu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuanYu, ZhangFei,ZhaoYun,HuangZhong,ZhugeLiang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HuangGai,SunCe,TaishiCi,HanDang,ZhouYu</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -257,9 +263,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -297,9 +303,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -332,9 +338,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -367,9 +390,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -641,7 +681,7 @@
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="62.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -685,6 +725,9 @@
       <c r="B3" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -697,7 +740,7 @@
         <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -709,6 +752,9 @@
       </c>
       <c r="B5" s="3" t="s">
         <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">

--- a/ExcelToJSONConverter/excel/region.xlsx
+++ b/ExcelToJSONConverter/excel/region.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043F41A1-8746-4A8F-B7CE-7B6237AA10F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB43369-DA90-40AF-8B97-EA0869869918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="285" yWindow="2775" windowWidth="16200" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -89,14 +89,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Wei</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Shu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>촉</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -109,10 +101,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Wu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>master</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -142,6 +130,18 @@
   </si>
   <si>
     <t>HuangGai,SunCe,TaishiCi,HanDang,ZhouYu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WEI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WU</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -692,13 +692,13 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -715,32 +715,32 @@
         <v>0</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -748,13 +748,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">

--- a/ExcelToJSONConverter/excel/region.xlsx
+++ b/ExcelToJSONConverter/excel/region.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB43369-DA90-40AF-8B97-EA0869869918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6D7FEF-D526-4D6F-8CE8-E25DDCCB9661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -143,6 +143,13 @@
   <si>
     <t>WU</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CaoCao</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SunQuan</t>
   </si>
 </sst>
 </file>
@@ -725,6 +732,9 @@
       <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="C3" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="D3" t="s">
         <v>23</v>
       </c>
@@ -752,6 +762,9 @@
       </c>
       <c r="B5" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
       </c>
       <c r="D5" t="s">
         <v>25</v>

--- a/ExcelToJSONConverter/excel/region.xlsx
+++ b/ExcelToJSONConverter/excel/region.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6D7FEF-D526-4D6F-8CE8-E25DDCCB9661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1328FD2-7182-4B45-83B1-00703EA005E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>

--- a/ExcelToJSONConverter/excel/region.xlsx
+++ b/ExcelToJSONConverter/excel/region.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1328FD2-7182-4B45-83B1-00703EA005E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CF0C75-BC11-4ADD-A646-EE1CC1C9CFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20325" yWindow="1515" windowWidth="16200" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -738,6 +738,9 @@
       <c r="D3" t="s">
         <v>23</v>
       </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -768,6 +771,9 @@
       </c>
       <c r="D5" t="s">
         <v>25</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
